--- a/Todos_Archivos_procesados.xlsx
+++ b/Todos_Archivos_procesados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,25 +506,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Sub total CCF</t>
+          <t>Sub Total CCF</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Total IVA</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Total CCF</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Nombre del archivo</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Correo Receptor</t>
         </is>
@@ -589,18 +594,21 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Retención 1% IVA s/CCF DTE6804 CENTRAL DE RODAMIENTOS</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0178483A-CC0C-406B-8D75-56A23E141CDF.json</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>informacion@cerosa.com</t>
         </is>
@@ -665,14 +673,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>08C47A1E-489B-4747-96BF-BDBA13D427F9.json</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -737,14 +748,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>08C47A1E-489B-4747-96BF-BDBA13D427F9.json</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -809,18 +823,21 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>CCF-649AAA12-D3CD-4B85-A5D7-F590AA9BEE26</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>09C6487E-B719-434C-BBFE-CC60313942DB.json</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -882,19 +899,26 @@
       <c r="O6" t="n">
         <v>4.8</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>FIJADOR P/PERNO LOCTITE  # 271     6ml</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0B40C520-6B97-4E84-92DF-35A8D29EA4BA.json</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -956,19 +980,26 @@
       <c r="O7" t="n">
         <v>0.06</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>PRISIONERO ALLEN M/M  6 X 6</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0B40C520-6B97-4E84-92DF-35A8D29EA4BA.json</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -1030,19 +1061,26 @@
       <c r="O8" t="n">
         <v>0.08</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>PRISIONERO ALLEN M/M  6 X 10</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0B40C520-6B97-4E84-92DF-35A8D29EA4BA.json</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -1104,19 +1142,24 @@
       <c r="O9" t="n">
         <v>5890</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="P9" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>115BBDE7-2265-4FDD-8DA9-4D7FBCB8E58F.json</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -1181,18 +1224,21 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Comprobante CRE</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>13B5D334-13CE-48AD-AE24-7D8497D38E32.json</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1257,18 +1303,21 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>IVA 1% Anticipo: 08D1D650-4F39</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>15F0FD55-2D8D-45AC-A065-C21F98126780.json</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1333,14 +1382,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1405,14 +1457,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1477,14 +1532,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1546,19 +1604,26 @@
       <c r="O15" t="n">
         <v>5890</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="P15" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6596.8</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>1C06FFA3-07CE-4F9A-94AF-6611F75A4EA7.json</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -1623,18 +1688,21 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>CPRA. 2 GABINETE ACERO INOX 300X200X150</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>1F001ABE-6976-4E68-8816-5007EF3F1651.json</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1699,18 +1767,21 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000006470</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>1P001-00000000000647006141511770020.json</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1775,18 +1846,21 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000006471</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>1P001-00000000000647106141511770020.json</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1851,18 +1925,21 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000006473</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>1P001-00000000000647306141511770020.json</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -1927,18 +2004,21 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000006510</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1P001-00000000000651006141511770020.json</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2003,18 +2083,21 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000006513</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>1P001-00000000000651306141511770020.json</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2079,18 +2162,21 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Retenci?n al documento DTE-03-M001P001-000000000007244</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>1P001-00000000000724406141511770020.json</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2152,19 +2238,26 @@
       <c r="O23" t="n">
         <v>4.5</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="P23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>RETENEDOR</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>23159F04-1D92-4864-8484-1B89FE2A21EB.json</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -2226,19 +2319,26 @@
       <c r="O24" t="n">
         <v>22.95</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="P24" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R24" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>243B9134-1B15-4645-AB77-045BFC25384D.json</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -2303,18 +2403,21 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>CCF-21D0B3C4-DC41-4AAC-9BD4-51A36B490AC0</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>264724A6-8A93-4752-97A5-1AAC6AE3719B.json</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2379,18 +2482,21 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>CCF-BAAE81D4-56E4-4B8F-B925-6A4139E9460F</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>269A17A2-4029-4487-B494-F488358DDF5E.json</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2455,14 +2561,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
         <is>
           <t>27E379B7-1B83-4C64-ADC0-5C83806A597A.json</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2527,14 +2636,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
         <is>
           <t>283B5113-C01B-46D1-A890-CD00F9A8E2F8.json</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -2599,18 +2711,21 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
         <is>
           <t>Item 1</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -2675,18 +2790,21 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>Item 2</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -2751,18 +2869,21 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>Item 3</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -2827,18 +2948,21 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>Item 4</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -2903,18 +3027,21 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Item 5</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -2979,18 +3106,21 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
         <is>
           <t>Item 6</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -3055,18 +3185,21 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>Item 7</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>carmen.zavaleta@cerosa.com</t>
         </is>
@@ -3128,19 +3261,26 @@
       <c r="O36" t="n">
         <v>115.5</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
+      <c r="P36" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>130.51</v>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>389D2801-2C0B-42D7-9CCB-DEA24161499E.json</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -3205,18 +3345,21 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
         <is>
           <t>CCF-40420D7C-093D-4296-B2A6-6A8188B4E3F5</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>397F2380-4487-4AD8-879A-8B21608BC008.json</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -3278,19 +3421,26 @@
       <c r="O38" t="n">
         <v>47.88</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
+      <c r="P38" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="R38" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>FAJA</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>3EBE2A93-5BBC-4718-B4EB-229F66F9B22B.json</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -3352,19 +3502,26 @@
       <c r="O39" t="n">
         <v>302.2</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
+      <c r="P39" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="R39" t="n">
+        <v>341.49</v>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>FAJA</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>3F4AFD0B-F68C-43E8-A368-BC9F65362285.json</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -3429,18 +3586,21 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
         <is>
           <t>Retención 1% IVA s/CCF DTE6803 CENTRAL DE RODAMIENTOS</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>3F66EE72-42CE-429A-ADD7-479231E99B71.json</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>informacion@cerosa.com</t>
         </is>
@@ -3505,18 +3665,21 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
         <is>
           <t>RETENCION DEL 1% SEGUN FACTURACION AMPARADA EN EL QUEDAN No 202509523</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>43043AD5-35CE-4FCF-E064-00144FF8838D.json</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>liliana.martinez@cerosa.com</t>
         </is>
@@ -3581,18 +3744,21 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
         <is>
           <t>RETENCION DEL 1% SEGUN FACTURACION AMPARADA EN EL QUEDAN No 202509605</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>43535047-9E86-17F6-E064-00144FF8838D.json</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>liliana.martinez@cerosa.com</t>
         </is>
@@ -3657,14 +3823,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
         <is>
           <t>4F3DC115-3B92-4484-830F-BC316CED7AE6.json</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -3729,18 +3898,21 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
         <is>
           <t>Retención IVA 1%</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>50500DA2-6BC8-4588-8F2A-36BF6F3D83A7.json</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -3805,18 +3977,21 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
         <is>
           <t>FD7D485B-B79D-451F-A783-5E07742FAA0E</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>5261228E-5188-4F4C-8D03-B83CB26DFF85.json</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -3878,19 +4053,26 @@
       <c r="O46" t="n">
         <v>13.8</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
+      <c r="P46" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R46" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>CANDADO</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>5839E27F-5702-4CED-89E9-0A19DE35F6AC.json</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -3952,19 +4134,26 @@
       <c r="O47" t="n">
         <v>166.9</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
+      <c r="P47" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R47" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>C158 - FAJA V HI-POWER 162.39" (24mm) GATES</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>5F6145CA-1AE2-2853-9D1C-5448063F4BB2.json</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -4029,18 +4218,21 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
         <is>
           <t xml:space="preserve">BIENES            </t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>61EDE671-97A2-412A-8392-8F6B44C904F2.json</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>raul.gonzalez@cerosa.com</t>
         </is>
@@ -4105,18 +4297,21 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
         <is>
           <t>CCF-70DC28D7D4B248F789C5EF0283D7AAE7</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>6224EF1E-CFB5-4FE7-9C6C-A9DCF836AB87.json</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -4178,19 +4373,26 @@
       <c r="O50" t="n">
         <v>120</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="P50" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="R50" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>Rosca M10 x 1.5 a centro de cam follower segun indicaciones</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>6254DC64-2B31-440C-A6FA-EF8267CE475E.json</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -4255,18 +4457,21 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 496737519086</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-AEB2-808000245862.json</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4331,18 +4536,21 @@
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF EAF4980B126E</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-AEB2-828000245863.json</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4407,18 +4615,21 @@
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF F2653ABEC4F9</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B09C-A98000246506.json</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4483,18 +4694,21 @@
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 7A8319D186E7</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B09C-AE8000246507.json</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4559,18 +4773,21 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 4740CCF8828A</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B09C-B28000246508.json</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4635,18 +4852,21 @@
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 3B2C267AD7F4</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B1B0-E68000246623.json</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4711,18 +4931,21 @@
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 5D4378106E63</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B1B1-C68000246695.json</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4787,18 +5010,21 @@
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 79B16578D517</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B393-538000247174.json</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4863,18 +5089,21 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF D56D0E4A2308</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B393-568000247175.json</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -4939,18 +5168,21 @@
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 9BB4EB7708E5</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B395-6B8000247295.json</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5015,18 +5247,21 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 6AAB19783B71</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B395-6E8000247296.json</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5091,18 +5326,21 @@
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF F05075AB3E2B</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B395-708000247297.json</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5167,18 +5405,21 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF A05818319836</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B395-738000247298.json</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5243,18 +5484,21 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
         <is>
           <t>Aplicado a Compra con CCF 4796487851ED</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>63995E65-FA18-1FD0-B395-758000247299.json</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5316,19 +5560,26 @@
       <c r="O65" t="n">
         <v>10.39</v>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
+      <c r="P65" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R65" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>FAJA B75 BANDO</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>672D6737-AFC6-4935-B41C-445903423A39.json</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Facturacionelectronica@cerosa.com</t>
         </is>
@@ -5393,18 +5644,21 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
         <is>
           <t xml:space="preserve">BIENES            </t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>6B473887-EE07-45F0-B6D3-12DF19C9B934.json</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>raul.gonzalez@cerosa.com</t>
         </is>
@@ -5466,19 +5720,24 @@
       <c r="O67" t="n">
         <v>5890</v>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
+      <c r="P67" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>6F3EC5DD-FE11-4A56-ABF8-5052DDFAADDD.json</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -5543,18 +5802,21 @@
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
         <is>
           <t>CPRA. GABINETE ACERO/AUTOMATO/MANETA DE</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>70F448C6-F7DF-415F-A3FE-C737208057E8.json</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5619,18 +5881,21 @@
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
         <is>
           <t>CPRA. FAJA S18/30 4780 X 60 MM PARA DESP</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>7146F7AD-C19D-4A89-90C4-BEFC70AE03CA.json</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5695,18 +5960,21 @@
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
         <is>
           <t>2FFDFA99-AD06-47BA-AF0F-7486E6DB40F1</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>71954747-81F4-4FBE-BF8F-4B8B171FECF1.json</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5768,19 +6036,26 @@
       <c r="O71" t="n">
         <v>2427.18</v>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
+      <c r="P71" t="n">
+        <v>2427.18</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2742.71</v>
+      </c>
+      <c r="S71" t="inlineStr">
         <is>
           <t>HONORARIOS POR SERVICIOS PROFESIONALES MES DE DICIEMBRE 2025</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>787928DA-ED91-4755-80D6-0E43EADA8BA0.json</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>cesar.garcia@cerosa.com</t>
         </is>
@@ -5845,14 +6120,17 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
       <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr">
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
         <is>
           <t>79157784-11AD-4903-B5F6-EB9A39E20377.json</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5917,18 +6195,21 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
         <is>
           <t>CCF-E6C5EF48-58DE-40A9-9AF1-645051F98E6B</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>7D41829A-DE48-4C50-9030-B192AF151C77.json</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -5993,14 +6274,17 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
       <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr">
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
         <is>
           <t>80A7EEC7-577E-4D91-8401-2689379D89C4.json</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6065,18 +6349,21 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
         <is>
           <t>DTE2025-7153</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>83CF9CF3-7D3A-4352-B3BA-72BCA15BF460.json</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6123,18 +6410,21 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr">
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
         <is>
           <t>CUOTAS ESTUDIANTES BECADOS</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>859885B7-81DE-4E25-8AF8-FAE06ECA07FF.json</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6195,18 +6485,21 @@
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
         <is>
           <t>CCF 8CDA6757-2EBB-4A34-B292-01E639525200 del 29/10/2025</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>86B872B3-7509-4495-9187-4279F27A1B2D.json</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -6271,18 +6564,21 @@
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
         <is>
           <t>AUTOMATO O GUARDAMOTOR PARA CUARTO FRIO DE LA BODEGA CENTRAL MICOMI</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>86EFF862-3248-4FC5-B92D-16C67247A852.json</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>informacion@cerosa.com</t>
         </is>
@@ -6347,18 +6643,21 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
         <is>
           <t>CCF-1A81600C-D0A4-4CBB-B4FF-0E8ACADBE927</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>888A968D-CE20-41EE-87F2-D6F70A9FB151.json</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6423,18 +6722,21 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
         <is>
           <t>CPRA. FAJA S18/30 4780 X 60 MM P/DESPLUM</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>889B95B5-3382-4C46-8E3F-801AA358EA71.json</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6499,18 +6801,21 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
         <is>
           <t>DTE-03-7521</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7.json</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6575,18 +6880,21 @@
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
         <is>
           <t>DTE-03-7232</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7.json</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6651,14 +6959,17 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
       <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
         <is>
           <t>8D963F4A-24DB-43CB-A4FC-B8B129B6152F.json</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -6720,19 +7031,26 @@
       <c r="O84" t="n">
         <v>651.66</v>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
+      <c r="P84" t="n">
+        <v>651.66</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="R84" t="n">
+        <v>736.38</v>
+      </c>
+      <c r="S84" t="inlineStr">
         <is>
           <t>SERVICIO DE LIMPIEZA DEL MES DE DICIEMBRE 2025</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>933A63F8-FD8A-4595-97F4-93FFDEA88CE3.json</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -6794,19 +7112,26 @@
       <c r="O85" t="n">
         <v>94.25</v>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
+      <c r="P85" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="R85" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="S85" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>949E828F-D67A-4472-B14D-3DCF0DB40415.json</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -6868,19 +7193,26 @@
       <c r="O86" t="n">
         <v>12.23</v>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
+      <c r="P86" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R86" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="S86" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>9C12B13A-A617-4D21-A07C-084AE61789F1.json</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -6942,19 +7274,26 @@
       <c r="O87" t="n">
         <v>16.91</v>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr">
+      <c r="P87" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R87" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="S87" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>9C12B13A-A617-4D21-A07C-084AE61789F1.json</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -7016,19 +7355,26 @@
       <c r="O88" t="n">
         <v>5890</v>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr">
+      <c r="P88" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6596.8</v>
+      </c>
+      <c r="S88" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>9C610C5D-92C9-4FE2-8C7F-578AC90854A9.json</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -7093,14 +7439,17 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
       <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr">
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
         <is>
           <t>A3D11227-70B9-4D40-81E5-8901ABF6A766.json</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7165,19 +7514,22 @@
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
         <is>
           <t xml:space="preserve">4-0860-5M-JASON Manga de sincronismo, 860-5M, Longitud externa 860 mm, numero de
 dientes 172, jason 30 mms </t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>A46D4E64-4485-41B4-8248-152D2E98DD72.json</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7242,18 +7594,21 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
         <is>
           <t>CPRA. FAJA S250.160.00 X 6.00CM.P/DESCOL</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>A91B7DF7-81AE-4934-9194-8B9FEC3046C5.json</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7318,18 +7673,21 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
         <is>
           <t>RET 1% CCFDTE030000007514 17/11/2025</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>ABF1227C-1FCA-43A4-817B-DB4D94FEAF04.json</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7394,18 +7752,21 @@
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr">
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
         <is>
           <t>CHUMACERAS PARA SANDER DE MAQUINAS TREFILADORAS. Basado en Solicitud de compra 2274. Basado en Pedidos 4108. CODIGO Basado en Pedido de entrada de mercancías 3960.</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>AF03CD2B-9D09-4F97-80E8-7AB66E843F99.json</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7470,18 +7831,21 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
         <is>
           <t>CPRA. MATERIALES P/USO MODIFICACION Y TR</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>B048B404-7A75-4503-B491-A6EDFF789AD4.json</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7546,18 +7910,21 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
         <is>
           <t>CCF-C487C262-D03B-4319-BE35-48F565F6CEDF</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>B52270FA-58B8-472D-AE09-355D447A5CF2.json</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7622,14 +7989,17 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
         <is>
           <t>B73C67D4-F513-4199-8329-4B1062067E81.json</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7691,19 +8061,26 @@
       <c r="O97" t="n">
         <v>419.42</v>
       </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
+      <c r="P97" t="n">
+        <v>419.42</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="R97" t="n">
+        <v>473.94</v>
+      </c>
+      <c r="S97" t="inlineStr">
         <is>
           <t>DIETAS MES DE DICIEMBRE 2025</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>B81DCACE-B766-49BF-9628-4DF221F05922.json</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>cesar.garcia@cerosa.com</t>
         </is>
@@ -7768,14 +8145,17 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr">
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
         <is>
           <t>BF2BA5D5-9582-42EC-99C8-42DB67284886.json</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7840,18 +8220,21 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
         <is>
           <t>CPRA. MATERIALES P/USO MODIFICACION Y TR</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>BFCC3EFC-4BDD-4A5E-AD2E-F50AD0D44631.json</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -7913,19 +8296,26 @@
       <c r="O100" t="n">
         <v>19.07</v>
       </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr">
+      <c r="P100" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R100" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="S100" t="inlineStr">
         <is>
           <t>BAL. 3</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>C05AFC5D-3407-4668-8826-68D3B3C4683E.json</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -7987,19 +8377,26 @@
       <c r="O101" t="n">
         <v>5890</v>
       </c>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr">
+      <c r="P101" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6596.8</v>
+      </c>
+      <c r="S101" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>C205B00E-A61F-476F-AEBE-81E97844A178.json</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -8061,19 +8458,26 @@
       <c r="O102" t="n">
         <v>225</v>
       </c>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr">
+      <c r="P102" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="R102" t="n">
+        <v>306.63</v>
+      </c>
+      <c r="S102" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="T102" t="inlineStr">
         <is>
           <t>C565FBB3-6E06-406F-959B-11A7087C7A4E.json</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -8135,19 +8539,26 @@
       <c r="O103" t="n">
         <v>39</v>
       </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr">
+      <c r="P103" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="R103" t="n">
+        <v>306.63</v>
+      </c>
+      <c r="S103" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>C565FBB3-6E06-406F-959B-11A7087C7A4E.json</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="U103" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -8209,19 +8620,26 @@
       <c r="O104" t="n">
         <v>7.35</v>
       </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr">
+      <c r="P104" t="n">
+        <v>271.35</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="R104" t="n">
+        <v>306.63</v>
+      </c>
+      <c r="S104" t="inlineStr">
         <is>
           <t>ARANDELA</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>C565FBB3-6E06-406F-959B-11A7087C7A4E.json</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -8286,18 +8704,21 @@
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr">
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
         <is>
           <t>Documento Relacionado 871B748E-509E-4E94-9AD9-76552DA98410</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>C5D598D6-0748-4E1A-B57E-4B35189EBBF4.json</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -8362,18 +8783,21 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr">
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
         <is>
           <t>CCF-E3C6F01A-18A9-4F2A-BFA2-4A9CFE55DE64</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>C6E2AB93-65FA-4E40-AC6E-59AE8CC63431.json</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -8438,18 +8862,21 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr">
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
         <is>
           <t>B58F50D5-A0E2-47C0-A4E2-89A3C9D37991</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>CA105E91-D16E-40A5-BF95-76BF0E5A8C84.json</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="U107" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -8514,18 +8941,21 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr">
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
+      <c r="T108" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON (2).json</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="U108" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8590,18 +9020,21 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr">
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON (2).json</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8666,18 +9099,21 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="T110" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON (3).json</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="U110" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8742,18 +9178,21 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr">
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
+      <c r="T111" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON (3).json</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="U111" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8818,18 +9257,21 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr">
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
+      <c r="T112" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON.json</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="U112" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8894,18 +9336,21 @@
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr">
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
+      <c r="T113" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON.json</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="U113" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -8970,18 +9415,21 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr">
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
+      <c r="T114" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON_1.json</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="U114" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -9046,18 +9494,21 @@
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
         <is>
           <t>Bienes</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
+      <c r="T115" t="inlineStr">
         <is>
           <t>COMPRETENCION_1_JSON_1.json</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="U115" t="inlineStr">
         <is>
           <t>SILVIA.ARCE@CEROSA.COM</t>
         </is>
@@ -9104,18 +9555,21 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr">
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
         <is>
           <t>DONACION MES DE NOVIEMBRE 2025</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
+      <c r="T116" t="inlineStr">
         <is>
           <t>COMPROBANTE_DE_DONACION-0614-151177-002-0-707242D3-ECD0-4DF9-ACD3-67D6A3644044.json</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9176,18 +9630,21 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr">
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
         <is>
           <t>Retención IVA 1%</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
+      <c r="T117" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-2B22166E-FC8D-49C7-A20E-D0814F17C2EC.json</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="U117" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9252,18 +9709,21 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr">
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
         <is>
           <t>Retención IVA 1%</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
+      <c r="T118" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-2B22166E-FC8D-49C7-A20E-D0814F17C2EC.json</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="U118" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9328,18 +9788,21 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr">
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="T119" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="U119" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9404,18 +9867,21 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr">
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
+      <c r="T120" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="U120" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9480,18 +9946,21 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr">
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="T121" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="U121" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9556,18 +10025,21 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr">
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
+      <c r="T122" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="U122" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9632,18 +10104,21 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr">
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
+      <c r="T123" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="U123" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9708,18 +10183,21 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr">
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
         <is>
           <t>Retención 1% Oct25</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
+      <c r="T124" t="inlineStr">
         <is>
           <t>Comprobante_Electronico-F554889F-6589-4F74-9F50-B1A91EC6254C.json</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="U124" t="inlineStr">
         <is>
           <t>Silvia.arce@cerosa.com</t>
         </is>
@@ -9781,19 +10259,26 @@
       <c r="O125" t="n">
         <v>2.1</v>
       </c>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr">
+      <c r="P125" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S125" t="inlineStr">
         <is>
           <t>RETENEDOR</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
+      <c r="T125" t="inlineStr">
         <is>
           <t>D0E2BADC-ED8B-4105-AA7F-CA6C4CD2889F.json</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="U125" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -9855,19 +10340,26 @@
       <c r="O126" t="n">
         <v>5890</v>
       </c>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr">
+      <c r="P126" t="n">
+        <v>5890</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>765.7</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6596.8</v>
+      </c>
+      <c r="S126" t="inlineStr">
         <is>
           <t>RA10X16V1-WS1-E95841 Valvula compuerta cuadrada 16", incluye Entrada de servicio HISS-10X16-E95780, Control de aire 4M375-24ES1-24VDC, Valvula 4LV375, Interruptor magnetico 4CC1A-SPST</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
+      <c r="T126" t="inlineStr">
         <is>
           <t>D39DC43D-2750-460B-8EFF-ECAAB9CA66DC.json</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="U126" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -9932,18 +10424,21 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr">
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
         <is>
           <t>CPRA. 1 INTERRUCTOR TERMOMAGNECTICO 40A</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
+      <c r="T127" t="inlineStr">
         <is>
           <t>D470AB26-351E-49E0-B4AE-FEB0B7EB231D.json</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="U127" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -10008,14 +10503,17 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
       <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr">
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
         <is>
           <t>D6B39A84-23B5-407E-B820-B292D1D152A0.json</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="U128" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -10077,19 +10575,26 @@
       <c r="O129" t="n">
         <v>2160</v>
       </c>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
+      <c r="P129" t="n">
+        <v>2160</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2419.2</v>
+      </c>
+      <c r="S129" t="inlineStr">
         <is>
           <t>RS125J30/750NC-CAJA Grapa metál.30"(Jgo)p/banda 3.2-4.8mm espsr.d/polea 3"</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
+      <c r="T129" t="inlineStr">
         <is>
           <t>D9D08459-A210-4E50-B4D4-A15AF613CBD5.json</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="U129" t="inlineStr">
         <is>
           <t>cmi-ventanillafisicasv@somoscmi.com</t>
         </is>
@@ -10154,18 +10659,21 @@
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr">
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
         <is>
           <t>CCF 4D558DE1-62A9-46D6-9DC6-6A8120A485AF del 08/11/2025</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
+      <c r="T130" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="U130" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10230,18 +10738,21 @@
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr">
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
         <is>
           <t>CCF B28377CD-04ED-41D5-BE67-E1C30C5F2A0A del 13/11/2025</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
+      <c r="T131" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10306,18 +10817,21 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr">
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
         <is>
           <t>CCF D59AFDC5-E4DF-461F-AF6C-39FD1CA0A1B3 del 27/11/2025</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
+      <c r="T132" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="U132" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10382,18 +10896,21 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr">
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
         <is>
           <t>CCF 9F8F173A-63DC-4921-B42C-33D1637F5A55 del 27/11/2025</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
+      <c r="T133" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="U133" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10458,18 +10975,21 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr">
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
         <is>
           <t>CCF 1D65F344-AD5C-4F05-BC5C-D01DB181243E del 27/11/2025</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
+      <c r="T134" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="U134" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10534,18 +11054,21 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr">
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
         <is>
           <t>CCF 2AD4FBC3-82BF-42AB-A6C7-C5D16A327F82 del 27/11/2025</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
+      <c r="T135" t="inlineStr">
         <is>
           <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="U135" t="inlineStr">
         <is>
           <t xml:space="preserve">silvia.arce@cerosa.com </t>
         </is>
@@ -10607,19 +11130,26 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr">
+      <c r="P136" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="S136" t="inlineStr">
         <is>
           <t>COBRO POR M3 CONSUMIDO</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
+      <c r="T136" t="inlineStr">
         <is>
           <t>DBCAF93A-4A86-4BD6-9E94-96789E7A21C5.json</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="U136" t="inlineStr">
         <is>
           <t>jonatan.vasquez@cerosa.com</t>
         </is>
@@ -10681,19 +11211,26 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr">
+      <c r="P137" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="S137" t="inlineStr">
         <is>
           <t>SERVICIOS DE ALCANTARILLADOS</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
+      <c r="T137" t="inlineStr">
         <is>
           <t>DBCAF93A-4A86-4BD6-9E94-96789E7A21C5.json</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>jonatan.vasquez@cerosa.com</t>
         </is>
@@ -10758,14 +11295,17 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr">
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr">
         <is>
           <t>DC7C7B8F-1405-49F7-AA31-A4AAFBC87EBE.json</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="U138" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -10827,19 +11367,26 @@
       <c r="O139" t="n">
         <v>69.3</v>
       </c>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr">
+      <c r="P139" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="R139" t="n">
+        <v>78.31</v>
+      </c>
+      <c r="S139" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
+      <c r="T139" t="inlineStr">
         <is>
           <t>DF24FB74-7E2B-4EEC-9028-E5A0DD22021F.json</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="U139" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -10901,19 +11448,26 @@
       <c r="O140" t="n">
         <v>17.69911504</v>
       </c>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr">
+      <c r="P140" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R140" t="n">
+        <v>40</v>
+      </c>
+      <c r="S140" t="inlineStr">
         <is>
           <t>SERVICIO DE MONITOREO DE ALARMA, MES DE  DICIEMBRE DE 2025, BODEGA</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
+      <c r="T140" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000000377 - 37 CENTRAL DE RODAMIENTO, S.A. DE C.V.json</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="U140" t="inlineStr">
         <is>
           <t>FACTURACIONELECTRONICA@CEROSA.COM</t>
         </is>
@@ -10975,19 +11529,26 @@
       <c r="O141" t="n">
         <v>17.69911504</v>
       </c>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr">
+      <c r="P141" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>40</v>
+      </c>
+      <c r="S141" t="inlineStr">
         <is>
           <t>SERVICIO DE MONITOREO DE ALARMA, MES DE  DICIEMBRE DE 2025, OFICINA</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
+      <c r="T141" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000000377 - 37 CENTRAL DE RODAMIENTO, S.A. DE C.V.json</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="U141" t="inlineStr">
         <is>
           <t>FACTURACIONELECTRONICA@CEROSA.COM</t>
         </is>
@@ -11049,19 +11610,26 @@
       <c r="O142" t="n">
         <v>132</v>
       </c>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr">
+      <c r="P142" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="R142" t="n">
+        <v>149.16</v>
+      </c>
+      <c r="S142" t="inlineStr">
         <is>
           <t>656-8M-25 FAJA SINCRONISMO</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
+      <c r="T142" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000006881-2025-11-22.json</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="U142" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -11123,19 +11691,26 @@
       <c r="O143" t="n">
         <v>12</v>
       </c>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr">
+      <c r="P143" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R143" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="S143" t="inlineStr">
         <is>
           <t>SELLO MECANICO 1</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
+      <c r="T143" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000006945-2025-11-25.json</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="U143" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11197,19 +11772,26 @@
       <c r="O144" t="n">
         <v>40</v>
       </c>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr">
+      <c r="P144" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R144" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="S144" t="inlineStr">
         <is>
           <t>BALERO SKF ALTA TEMPERATURA</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
+      <c r="T144" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007047-2025-12-01.json</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="U144" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11271,19 +11853,26 @@
       <c r="O145" t="n">
         <v>32.65</v>
       </c>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr">
+      <c r="P145" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="R145" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="S145" t="inlineStr">
         <is>
           <t>POLEA DE ALUMINIO</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
+      <c r="T145" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007097-2025-12-02.json</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="U145" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11345,19 +11934,26 @@
       <c r="O146" t="n">
         <v>214.2</v>
       </c>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr">
+      <c r="P146" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="R146" t="n">
+        <v>242.05</v>
+      </c>
+      <c r="S146" t="inlineStr">
         <is>
           <t>BALERO AGUJA 55X72X22</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
+      <c r="T146" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007114-2025-12-02.json</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="U146" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11419,19 +12015,26 @@
       <c r="O147" t="n">
         <v>751.2</v>
       </c>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr">
+      <c r="P147" t="n">
+        <v>794.39</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>103.27</v>
+      </c>
+      <c r="R147" t="n">
+        <v>897.66</v>
+      </c>
+      <c r="S147" t="inlineStr">
         <is>
           <t>BALERO SKF</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
+      <c r="T147" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007131-2025-12-03.json</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="U147" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11493,19 +12096,26 @@
       <c r="O148" t="n">
         <v>43.19</v>
       </c>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr">
+      <c r="P148" t="n">
+        <v>794.39</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>103.27</v>
+      </c>
+      <c r="R148" t="n">
+        <v>897.66</v>
+      </c>
+      <c r="S148" t="inlineStr">
         <is>
           <t>SEGUIDOR DE LEVAS 40mm (KR40PP)</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
+      <c r="T148" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007131-2025-12-03.json</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="U148" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11567,19 +12177,26 @@
       <c r="O149" t="n">
         <v>6</v>
       </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr">
+      <c r="P149" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="S149" t="inlineStr">
         <is>
           <t>RETENEDOR</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
+      <c r="T149" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007136-2025-12-03.json</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="U149" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11641,19 +12258,26 @@
       <c r="O150" t="n">
         <v>42</v>
       </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr">
+      <c r="P150" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="R150" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="S150" t="inlineStr">
         <is>
           <t>BALERO NTN 1 7/16 (SA207-23)</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
+      <c r="T150" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007159-2025-12-04.json</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="U150" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11715,19 +12339,26 @@
       <c r="O151" t="n">
         <v>388.71</v>
       </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr">
+      <c r="P151" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="R151" t="n">
+        <v>439.24</v>
+      </c>
+      <c r="S151" t="inlineStr">
         <is>
           <t>SEGUIDOR DE LEVAS 40mm (KR40PP)</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
+      <c r="T151" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007160-2025-12-04.json</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="U151" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11789,19 +12420,26 @@
       <c r="O152" t="n">
         <v>140</v>
       </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr">
+      <c r="P152" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="R152" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="S152" t="inlineStr">
         <is>
           <t>BALERO MACHILL</t>
         </is>
       </c>
-      <c r="S152" t="inlineStr">
+      <c r="T152" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007163-2025-12-04.json</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="U152" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11863,19 +12501,26 @@
       <c r="O153" t="n">
         <v>22</v>
       </c>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
+      <c r="P153" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R153" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="S153" t="inlineStr">
         <is>
           <t>CANDADOS P. AMER. 3/4</t>
         </is>
       </c>
-      <c r="S153" t="inlineStr">
+      <c r="T153" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007182-2025-12-04.json</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="U153" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -11937,19 +12582,26 @@
       <c r="O154" t="n">
         <v>12</v>
       </c>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
+      <c r="P154" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R154" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="S154" t="inlineStr">
         <is>
           <t>SELLO MECANICO 1</t>
         </is>
       </c>
-      <c r="S154" t="inlineStr">
+      <c r="T154" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007199-2025-12-05.json</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="U154" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12011,19 +12663,26 @@
       <c r="O155" t="n">
         <v>94.5</v>
       </c>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr">
+      <c r="P155" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="R155" t="n">
+        <v>106.79</v>
+      </c>
+      <c r="S155" t="inlineStr">
         <is>
           <t>FAJA</t>
         </is>
       </c>
-      <c r="S155" t="inlineStr">
+      <c r="T155" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007257-2025-12-08.json</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="U155" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12085,19 +12744,26 @@
       <c r="O156" t="n">
         <v>46.4</v>
       </c>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr">
+      <c r="P156" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="R156" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="S156" t="inlineStr">
         <is>
           <t>BALERO INA</t>
         </is>
       </c>
-      <c r="S156" t="inlineStr">
+      <c r="T156" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007266-2025-12-09.json</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="U156" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12159,19 +12825,26 @@
       <c r="O157" t="n">
         <v>60</v>
       </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr">
+      <c r="P157" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R157" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="S157" t="inlineStr">
         <is>
           <t>FAJA DUNLOP</t>
         </is>
       </c>
-      <c r="S157" t="inlineStr">
+      <c r="T157" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007295-2025-12-09.json</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="U157" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12233,19 +12906,26 @@
       <c r="O158" t="n">
         <v>42</v>
       </c>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr">
+      <c r="P158" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="R158" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="S158" t="inlineStr">
         <is>
           <t>BALERO SKF</t>
         </is>
       </c>
-      <c r="S158" t="inlineStr">
+      <c r="T158" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007302-2025-12-10.json</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="U158" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12307,19 +12987,26 @@
       <c r="O159" t="n">
         <v>60</v>
       </c>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr">
+      <c r="P159" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R159" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="S159" t="inlineStr">
         <is>
           <t>FAJA DUNLOP</t>
         </is>
       </c>
-      <c r="S159" t="inlineStr">
+      <c r="T159" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007326-2025-12-10.json</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="U159" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12381,19 +13068,26 @@
       <c r="O160" t="n">
         <v>87.75</v>
       </c>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
+      <c r="P160" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="R160" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="S160" t="inlineStr">
         <is>
           <t>FAJA INDUSTRIAL DUNLOP</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr">
+      <c r="T160" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007349-2025-12-11.json</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="U160" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12455,19 +13149,26 @@
       <c r="O161" t="n">
         <v>5.85</v>
       </c>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr">
+      <c r="P161" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="S161" t="inlineStr">
         <is>
           <t>FAJA INDUSTRIAL DUNLOP</t>
         </is>
       </c>
-      <c r="S161" t="inlineStr">
+      <c r="T161" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007350-2025-12-11.json</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr">
+      <c r="U161" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12529,19 +13230,26 @@
       <c r="O162" t="n">
         <v>18.5</v>
       </c>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr">
+      <c r="P162" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R162" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="S162" t="inlineStr">
         <is>
           <t>FAJA DUNLOP</t>
         </is>
       </c>
-      <c r="S162" t="inlineStr">
+      <c r="T162" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007483-2025-12-16.json</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
+      <c r="U162" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -12603,19 +13311,26 @@
       <c r="O163" t="n">
         <v>751.6</v>
       </c>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr">
+      <c r="P163" t="n">
+        <v>751.6</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="R163" t="n">
+        <v>849.3099999999999</v>
+      </c>
+      <c r="S163" t="inlineStr">
         <is>
           <t>BALERO NTN</t>
         </is>
       </c>
-      <c r="S163" t="inlineStr">
+      <c r="T163" t="inlineStr">
         <is>
           <t>DTE-03-M001P001-000000000007495-2025-12-17.json</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
+      <c r="U163" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -12677,19 +13392,26 @@
       <c r="O164" t="n">
         <v>184.68</v>
       </c>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr">
+      <c r="P164" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="R164" t="n">
+        <v>208.69</v>
+      </c>
+      <c r="S164" t="inlineStr">
         <is>
           <t>FACTURA DE SERVICIO.  (PERIODO FACTURADO 01/12/2025 - 31/12/2025)</t>
         </is>
       </c>
-      <c r="S164" t="inlineStr">
+      <c r="T164" t="inlineStr">
         <is>
           <t>dte-03-m001p0010000000000055401.json</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="U164" t="inlineStr">
         <is>
           <t>gerson.hernandez@cerosa.com</t>
         </is>
@@ -12751,19 +13473,24 @@
       <c r="O165" t="n">
         <v>30.5</v>
       </c>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr">
+      <c r="P165" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
         <is>
           <t>RETENEDOR</t>
         </is>
       </c>
-      <c r="S165" t="inlineStr">
+      <c r="T165" t="inlineStr">
         <is>
           <t>DTE-05-M001P001-000000000000191-2025-11-25.json</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
+      <c r="U165" t="inlineStr">
         <is>
           <t>facturaciónelectronica@cerosa.com</t>
         </is>
@@ -12828,18 +13555,21 @@
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr">
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
         <is>
           <t>RETENCIÓN DEL 1% IVA SEGÚN DTE CCF # 7334</t>
         </is>
       </c>
-      <c r="S166" t="inlineStr">
+      <c r="T166" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000000802_834D8746-25B5-4732-8190-7224DF226810.json</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="U166" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -12904,18 +13634,21 @@
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr">
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
         <is>
           <t>CR-19650-25</t>
         </is>
       </c>
-      <c r="S167" t="inlineStr">
+      <c r="T167" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000004701_3B4594F6-0426-4B60-993E-7ED951C0BAD1.json</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="U167" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -12980,18 +13713,21 @@
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr">
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
         <is>
           <t>CR-19651-25</t>
         </is>
       </c>
-      <c r="S168" t="inlineStr">
+      <c r="T168" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000004702_CC0997A7-3FBC-4900-BC44-C1F7377E1BDB.json</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="U168" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13056,18 +13792,21 @@
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr">
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
         <is>
           <t>CR-19653-25</t>
         </is>
       </c>
-      <c r="S169" t="inlineStr">
+      <c r="T169" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000004703_0E4E23E4-6253-4761-B28F-90115F9D40D9.json</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="U169" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13132,18 +13871,21 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr">
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
         <is>
           <t>CR-19663-25</t>
         </is>
       </c>
-      <c r="S170" t="inlineStr">
+      <c r="T170" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000004704_53993390-CCA0-4527-9AF8-F3016F93CFB7.json</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="U170" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13208,18 +13950,21 @@
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr">
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
         <is>
           <t>CR-19815-25</t>
         </is>
       </c>
-      <c r="S171" t="inlineStr">
+      <c r="T171" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000004735_FD8A1F21-5EB1-4BDC-A301-23872CFC7BDB.json</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="U171" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13284,18 +14029,21 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr">
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
         <is>
           <t>25/22271-CXP</t>
         </is>
       </c>
-      <c r="S172" t="inlineStr">
+      <c r="T172" t="inlineStr">
         <is>
           <t>DTE-07-M001P001-000000000005630_6BB96BEE-BF95-4829-B75A-001B5623B6B3.json</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="U172" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13360,18 +14108,21 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr">
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
         <is>
           <t>CCF#DTE-7354</t>
         </is>
       </c>
-      <c r="S173" t="inlineStr">
+      <c r="T173" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010170-2F1B8414-99C9-4277-B970-CB1C8B14B12C-10-11-2025 025523.json</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
+      <c r="U173" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13436,18 +14187,21 @@
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr">
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
         <is>
           <t>CCF#DTE-7506</t>
         </is>
       </c>
-      <c r="S174" t="inlineStr">
+      <c r="T174" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010461-9D020BB0-D298-4819-83AC-BEE2E40939CB-18-11-2025 021735.json</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
+      <c r="U174" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13512,18 +14266,21 @@
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr">
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
         <is>
           <t>CCF#DTE-7600</t>
         </is>
       </c>
-      <c r="S175" t="inlineStr">
+      <c r="T175" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010550-AEFC8F20-D47A-4EE3-AF07-A6AC06B88CF8-20-11-2025 024901.json</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
+      <c r="U175" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13588,18 +14345,21 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr">
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
         <is>
           <t>CCF#DTE-7661</t>
         </is>
       </c>
-      <c r="S176" t="inlineStr">
+      <c r="T176" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010707-27B0CB09-4F1C-4604-8E57-795B04E582B6-25-11-2025 101502.json</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
+      <c r="U176" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13664,18 +14424,21 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr">
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
         <is>
           <t>CCF#DTE-7670</t>
         </is>
       </c>
-      <c r="S177" t="inlineStr">
+      <c r="T177" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010707-27B0CB09-4F1C-4604-8E57-795B04E582B6-25-11-2025 101502.json</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
+      <c r="U177" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13740,18 +14503,21 @@
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr">
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
         <is>
           <t>CCF#DTE-7648</t>
         </is>
       </c>
-      <c r="S178" t="inlineStr">
+      <c r="T178" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
+      <c r="U178" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13816,18 +14582,21 @@
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr">
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
         <is>
           <t>CCF#DTE-7647</t>
         </is>
       </c>
-      <c r="S179" t="inlineStr">
+      <c r="T179" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="U179" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13892,18 +14661,21 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr">
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
         <is>
           <t>CCF#DTE-7646</t>
         </is>
       </c>
-      <c r="S180" t="inlineStr">
+      <c r="T180" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="U180" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -13968,18 +14740,21 @@
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr">
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
         <is>
           <t>CCF#DTE-7776</t>
         </is>
       </c>
-      <c r="S181" t="inlineStr">
+      <c r="T181" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010871-359910A9-A847-4F1C-88D2-A6CF961A9E52-28-11-2025 024944.json</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr">
+      <c r="U181" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14044,18 +14819,21 @@
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr">
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
         <is>
           <t>CCF#DTE-7779</t>
         </is>
       </c>
-      <c r="S182" t="inlineStr">
+      <c r="T182" t="inlineStr">
         <is>
           <t>DTE-07-M001P010-000000000010871-359910A9-A847-4F1C-88D2-A6CF961A9E52-28-11-2025 024944.json</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
+      <c r="U182" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14120,18 +14898,21 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr">
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
         <is>
           <t>Retención</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr">
+      <c r="T183" t="inlineStr">
         <is>
           <t>DTE-07-S003P001-000000000000106_7DA3A730-70AB-4897-BB57-D55831A9A9FC.json</t>
         </is>
       </c>
-      <c r="T183" t="inlineStr">
+      <c r="U183" t="inlineStr">
         <is>
           <t>informacion@cerosa.com</t>
         </is>
@@ -14193,19 +14974,26 @@
       <c r="O184" t="n">
         <v>45</v>
       </c>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr">
+      <c r="P184" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R184" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="S184" t="inlineStr">
         <is>
           <t>BAL. 4</t>
         </is>
       </c>
-      <c r="S184" t="inlineStr">
+      <c r="T184" t="inlineStr">
         <is>
           <t>E80D4731-4D33-4F20-A1AC-341C8A3DB2BE.json</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr">
+      <c r="U184" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -14270,18 +15058,21 @@
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr">
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
         <is>
           <t xml:space="preserve">Crédito Fiscal: </t>
         </is>
       </c>
-      <c r="S185" t="inlineStr">
+      <c r="T185" t="inlineStr">
         <is>
           <t>EC2A892C-5336-49BE-832F-4D2656FA682E.json</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
+      <c r="U185" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14343,19 +15134,26 @@
       <c r="O186" t="n">
         <v>14.04</v>
       </c>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr">
+      <c r="P186" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R186" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="S186" t="inlineStr">
         <is>
           <t>BALERO</t>
         </is>
       </c>
-      <c r="S186" t="inlineStr">
+      <c r="T186" t="inlineStr">
         <is>
           <t>EE8841FB-E9FB-4B1C-874D-C69AF5C00E58.json</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
+      <c r="U186" t="inlineStr">
         <is>
           <t>facturacionelectronica@cerosa.com</t>
         </is>
@@ -14420,18 +15218,21 @@
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr">
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr">
         <is>
           <t>CCF-79B9FC1B-4AF3-4EC4-B7D9-EB357255A187</t>
         </is>
       </c>
-      <c r="S187" t="inlineStr">
+      <c r="T187" t="inlineStr">
         <is>
           <t>EFA27456-B005-4F04-A1FD-EB72617BC038.json</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr">
+      <c r="U187" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14496,14 +15297,17 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
       <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr">
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr">
         <is>
           <t>F9EA6881-4E9A-40B9-B307-3C6213F4D3F8.json</t>
         </is>
       </c>
-      <c r="T188" t="inlineStr">
+      <c r="U188" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14568,18 +15372,21 @@
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr">
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
         <is>
           <t>SERVICIOS GENERALES</t>
         </is>
       </c>
-      <c r="S189" t="inlineStr">
+      <c r="T189" t="inlineStr">
         <is>
           <t>factura-DTE-07-M001P001-000000000008439.json</t>
         </is>
       </c>
-      <c r="T189" t="inlineStr">
+      <c r="U189" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14644,18 +15451,21 @@
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr">
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
         <is>
           <t>45984FC7-6E4B-4F7D-8558-4FFDF8194EF5</t>
         </is>
       </c>
-      <c r="S190" t="inlineStr">
+      <c r="T190" t="inlineStr">
         <is>
           <t>FC71A4F2-606A-4C12-968B-1C3F3F13E0E1.json</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
+      <c r="U190" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
@@ -14720,18 +15530,21 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr">
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
         <is>
           <t>no_aplica</t>
         </is>
       </c>
-      <c r="S191" t="inlineStr">
+      <c r="T191" t="inlineStr">
         <is>
           <t>FDFD466B-597B-4483-B341-C24123BC9ED9.json</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr">
+      <c r="U191" t="inlineStr">
         <is>
           <t>clientedte@agrosania.com</t>
         </is>
@@ -14796,14 +15609,17 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
       <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr">
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr">
         <is>
           <t>Retención No.4999.json</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr">
+      <c r="U192" t="inlineStr">
         <is>
           <t>silvia.arce@cerosa.com</t>
         </is>
